--- a/metalman-auto-engineer/backend/outputs/PFMEA_Result_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/PFMEA_Result_92187158.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1203,7 +1204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1349,7 +1350,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1509,9 +1510,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7009,7 +7007,7 @@
       <c r="S119" s="12" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="131" t="n">
+      <c r="A120" s="73" t="n">
         <v>45855</v>
       </c>
       <c r="B120" s="15" t="n"/>
@@ -7098,8 +7096,8 @@
       <c r="S122" s="7" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="n"/>
-      <c r="B123" s="12" t="n"/>
+      <c r="A123" s="81" t="n"/>
+      <c r="B123" s="82" t="n"/>
       <c r="C123" s="83" t="inlineStr">
         <is>
           <t>ACTION PLAN RULE : Action shall we taken if any RPN value crossed over 100 otherwise no need to take any action</t>
@@ -7354,7 +7352,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FAILURE MODE AND EFFECTS ANALYSIS (PROCESS FMEA)</t>
         </is>
       </c>
       <c r="D1" s="4" t="n"/>
@@ -7832,8 +7830,8 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="54" t="n"/>
       <c r="B13" s="54" t="n"/>
-      <c r="C13" s="54" t="n"/>
-      <c r="D13" s="54" t="n"/>
+      <c r="C13" s="119" t="n"/>
+      <c r="D13" s="119" t="n"/>
       <c r="E13" s="118" t="n"/>
       <c r="F13" s="118" t="n"/>
       <c r="G13" s="117" t="inlineStr">
@@ -7868,8 +7866,8 @@
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="54" t="n"/>
       <c r="B14" s="54" t="n"/>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="54" t="n"/>
+      <c r="C14" s="119" t="n"/>
+      <c r="D14" s="119" t="n"/>
       <c r="E14" s="118" t="n"/>
       <c r="F14" s="118" t="n"/>
       <c r="G14" s="117" t="inlineStr">
@@ -7904,8 +7902,8 @@
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="54" t="n"/>
       <c r="B15" s="54" t="n"/>
-      <c r="C15" s="55" t="n"/>
-      <c r="D15" s="55" t="n"/>
+      <c r="C15" s="119" t="n"/>
+      <c r="D15" s="119" t="n"/>
       <c r="E15" s="118" t="n"/>
       <c r="F15" s="118" t="n"/>
       <c r="G15" s="117" t="inlineStr">
@@ -7989,8 +7987,8 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="54" t="n"/>
       <c r="B17" s="54" t="n"/>
-      <c r="C17" s="54" t="n"/>
-      <c r="D17" s="54" t="n"/>
+      <c r="C17" s="119" t="n"/>
+      <c r="D17" s="119" t="n"/>
       <c r="E17" s="118" t="n"/>
       <c r="F17" s="118" t="n"/>
       <c r="G17" s="117" t="inlineStr">
@@ -8025,8 +8023,8 @@
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="54" t="n"/>
       <c r="B18" s="54" t="n"/>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="54" t="n"/>
+      <c r="C18" s="119" t="n"/>
+      <c r="D18" s="119" t="n"/>
       <c r="E18" s="118" t="n"/>
       <c r="F18" s="118" t="n"/>
       <c r="G18" s="117" t="inlineStr">
@@ -8061,8 +8059,8 @@
     <row r="19" ht="38" customHeight="1">
       <c r="A19" s="54" t="n"/>
       <c r="B19" s="54" t="n"/>
-      <c r="C19" s="55" t="n"/>
-      <c r="D19" s="55" t="n"/>
+      <c r="C19" s="119" t="n"/>
+      <c r="D19" s="119" t="n"/>
       <c r="E19" s="118" t="n"/>
       <c r="F19" s="118" t="n"/>
       <c r="G19" s="117" t="inlineStr">
@@ -8146,8 +8144,8 @@
     <row r="21" ht="47" customHeight="1">
       <c r="A21" s="54" t="n"/>
       <c r="B21" s="54" t="n"/>
-      <c r="C21" s="55" t="n"/>
-      <c r="D21" s="55" t="n"/>
+      <c r="C21" s="119" t="n"/>
+      <c r="D21" s="119" t="n"/>
       <c r="E21" s="118" t="n"/>
       <c r="F21" s="118" t="n"/>
       <c r="G21" s="117" t="inlineStr">
@@ -8231,8 +8229,8 @@
     <row r="23" ht="61" customHeight="1">
       <c r="A23" s="54" t="n"/>
       <c r="B23" s="54" t="n"/>
-      <c r="C23" s="55" t="n"/>
-      <c r="D23" s="55" t="n"/>
+      <c r="C23" s="119" t="n"/>
+      <c r="D23" s="119" t="n"/>
       <c r="E23" s="118" t="n"/>
       <c r="F23" s="118" t="n"/>
       <c r="G23" s="117" t="inlineStr">
@@ -8316,8 +8314,8 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="54" t="n"/>
       <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="54" t="n"/>
+      <c r="C25" s="119" t="n"/>
+      <c r="D25" s="119" t="n"/>
       <c r="E25" s="118" t="n"/>
       <c r="F25" s="118" t="n"/>
       <c r="G25" s="117" t="inlineStr">
@@ -8348,8 +8346,8 @@
     <row r="26" ht="38" customHeight="1">
       <c r="A26" s="55" t="n"/>
       <c r="B26" s="55" t="n"/>
-      <c r="C26" s="55" t="n"/>
-      <c r="D26" s="55" t="n"/>
+      <c r="C26" s="119" t="n"/>
+      <c r="D26" s="119" t="n"/>
       <c r="E26" s="118" t="n"/>
       <c r="F26" s="118" t="n"/>
       <c r="G26" s="117" t="inlineStr">
@@ -8439,8 +8437,8 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="55" t="n"/>
       <c r="B28" s="55" t="n"/>
-      <c r="C28" s="55" t="n"/>
-      <c r="D28" s="55" t="n"/>
+      <c r="C28" s="119" t="n"/>
+      <c r="D28" s="119" t="n"/>
       <c r="E28" s="118" t="n"/>
       <c r="F28" s="118" t="n"/>
       <c r="G28" s="117" t="inlineStr">
@@ -8526,8 +8524,8 @@
     <row r="30" ht="47" customHeight="1">
       <c r="A30" s="54" t="n"/>
       <c r="B30" s="54" t="n"/>
-      <c r="C30" s="55" t="n"/>
-      <c r="D30" s="55" t="n"/>
+      <c r="C30" s="119" t="n"/>
+      <c r="D30" s="119" t="n"/>
       <c r="E30" s="118" t="n"/>
       <c r="F30" s="118" t="n"/>
       <c r="G30" s="117" t="inlineStr">
@@ -8611,8 +8609,8 @@
     <row r="32" ht="54" customHeight="1">
       <c r="A32" s="54" t="n"/>
       <c r="B32" s="54" t="n"/>
-      <c r="C32" s="55" t="n"/>
-      <c r="D32" s="55" t="n"/>
+      <c r="C32" s="119" t="n"/>
+      <c r="D32" s="119" t="n"/>
       <c r="E32" s="118" t="n"/>
       <c r="F32" s="118" t="n"/>
       <c r="G32" s="117" t="inlineStr">
@@ -8696,8 +8694,8 @@
     <row r="34" ht="47" customHeight="1">
       <c r="A34" s="54" t="n"/>
       <c r="B34" s="54" t="n"/>
-      <c r="C34" s="55" t="n"/>
-      <c r="D34" s="55" t="n"/>
+      <c r="C34" s="119" t="n"/>
+      <c r="D34" s="119" t="n"/>
       <c r="E34" s="118" t="n"/>
       <c r="F34" s="118" t="n"/>
       <c r="G34" s="117" t="inlineStr">
@@ -8836,8 +8834,8 @@
     <row r="37" ht="47" customHeight="1">
       <c r="A37" s="54" t="n"/>
       <c r="B37" s="54" t="n"/>
-      <c r="C37" s="55" t="n"/>
-      <c r="D37" s="55" t="n"/>
+      <c r="C37" s="119" t="n"/>
+      <c r="D37" s="119" t="n"/>
       <c r="E37" s="118" t="n"/>
       <c r="F37" s="118" t="n"/>
       <c r="G37" s="117" t="inlineStr">
@@ -8921,8 +8919,8 @@
     <row r="39" ht="54" customHeight="1">
       <c r="A39" s="54" t="n"/>
       <c r="B39" s="54" t="n"/>
-      <c r="C39" s="55" t="n"/>
-      <c r="D39" s="55" t="n"/>
+      <c r="C39" s="119" t="n"/>
+      <c r="D39" s="119" t="n"/>
       <c r="E39" s="118" t="n"/>
       <c r="F39" s="118" t="n"/>
       <c r="G39" s="117" t="inlineStr">
@@ -9006,8 +9004,8 @@
     <row r="41" ht="47" customHeight="1">
       <c r="A41" s="54" t="n"/>
       <c r="B41" s="54" t="n"/>
-      <c r="C41" s="55" t="n"/>
-      <c r="D41" s="55" t="n"/>
+      <c r="C41" s="119" t="n"/>
+      <c r="D41" s="119" t="n"/>
       <c r="E41" s="118" t="n"/>
       <c r="F41" s="118" t="n"/>
       <c r="G41" s="117" t="inlineStr">
@@ -9464,8 +9462,8 @@
     <row r="50" ht="54" customHeight="1">
       <c r="A50" s="54" t="n"/>
       <c r="B50" s="54" t="n"/>
-      <c r="C50" s="55" t="n"/>
-      <c r="D50" s="55" t="n"/>
+      <c r="C50" s="119" t="n"/>
+      <c r="D50" s="119" t="n"/>
       <c r="E50" s="118" t="n"/>
       <c r="F50" s="118" t="n"/>
       <c r="G50" s="117" t="inlineStr">
@@ -9698,8 +9696,8 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="55" t="n"/>
       <c r="B55" s="55" t="n"/>
-      <c r="C55" s="55" t="n"/>
-      <c r="D55" s="55" t="n"/>
+      <c r="C55" s="119" t="n"/>
+      <c r="D55" s="119" t="n"/>
       <c r="E55" s="118" t="n"/>
       <c r="F55" s="118" t="n"/>
       <c r="G55" s="117" t="inlineStr">
@@ -9736,23 +9734,23 @@
           <t>Move for Next Process</t>
         </is>
       </c>
-      <c r="C56" s="58" t="n"/>
-      <c r="D56" s="58" t="n"/>
-      <c r="E56" s="58" t="n"/>
-      <c r="F56" s="58" t="n"/>
-      <c r="G56" s="58" t="n"/>
-      <c r="H56" s="58" t="n"/>
-      <c r="I56" s="58" t="n"/>
-      <c r="J56" s="58" t="n"/>
-      <c r="K56" s="58" t="n"/>
-      <c r="L56" s="58" t="n"/>
-      <c r="M56" s="58" t="n"/>
-      <c r="N56" s="58" t="n"/>
-      <c r="O56" s="58" t="n"/>
-      <c r="P56" s="58" t="n"/>
-      <c r="Q56" s="58" t="n"/>
-      <c r="R56" s="58" t="n"/>
-      <c r="S56" s="59" t="n"/>
+      <c r="C56" s="119" t="n"/>
+      <c r="D56" s="119" t="n"/>
+      <c r="E56" s="119" t="n"/>
+      <c r="F56" s="119" t="n"/>
+      <c r="G56" s="119" t="n"/>
+      <c r="H56" s="119" t="n"/>
+      <c r="I56" s="119" t="n"/>
+      <c r="J56" s="119" t="n"/>
+      <c r="K56" s="119" t="n"/>
+      <c r="L56" s="119" t="n"/>
+      <c r="M56" s="119" t="n"/>
+      <c r="N56" s="119" t="n"/>
+      <c r="O56" s="119" t="n"/>
+      <c r="P56" s="119" t="n"/>
+      <c r="Q56" s="119" t="n"/>
+      <c r="R56" s="119" t="n"/>
+      <c r="S56" s="119" t="n"/>
     </row>
     <row r="57" ht="39.9" customHeight="1">
       <c r="A57" s="120" t="inlineStr">
@@ -9869,7 +9867,7 @@
       <c r="T59" s="124" t="n"/>
     </row>
     <row r="60" ht="51" customHeight="1">
-      <c r="A60" s="131" t="n">
+      <c r="A60" s="73" t="n">
         <v>45855</v>
       </c>
       <c r="B60" s="15" t="n"/>
@@ -10614,8 +10612,8 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="54" t="n"/>
       <c r="B13" s="54" t="n"/>
-      <c r="C13" s="54" t="n"/>
-      <c r="D13" s="54" t="n"/>
+      <c r="C13" s="119" t="n"/>
+      <c r="D13" s="119" t="n"/>
       <c r="E13" s="118" t="n"/>
       <c r="F13" s="118" t="n"/>
       <c r="G13" s="117" t="inlineStr">
@@ -10650,8 +10648,8 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="54" t="n"/>
       <c r="B14" s="54" t="n"/>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="54" t="n"/>
+      <c r="C14" s="119" t="n"/>
+      <c r="D14" s="119" t="n"/>
       <c r="E14" s="118" t="n"/>
       <c r="F14" s="118" t="n"/>
       <c r="G14" s="117" t="inlineStr">
@@ -10686,8 +10684,8 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="54" t="n"/>
       <c r="B15" s="54" t="n"/>
-      <c r="C15" s="55" t="n"/>
-      <c r="D15" s="55" t="n"/>
+      <c r="C15" s="119" t="n"/>
+      <c r="D15" s="119" t="n"/>
       <c r="E15" s="118" t="n"/>
       <c r="F15" s="118" t="n"/>
       <c r="G15" s="117" t="inlineStr">
@@ -10771,8 +10769,8 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="54" t="n"/>
       <c r="B17" s="54" t="n"/>
-      <c r="C17" s="54" t="n"/>
-      <c r="D17" s="54" t="n"/>
+      <c r="C17" s="119" t="n"/>
+      <c r="D17" s="119" t="n"/>
       <c r="E17" s="118" t="n"/>
       <c r="F17" s="118" t="n"/>
       <c r="G17" s="117" t="inlineStr">
@@ -10807,8 +10805,8 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="54" t="n"/>
       <c r="B18" s="54" t="n"/>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="54" t="n"/>
+      <c r="C18" s="119" t="n"/>
+      <c r="D18" s="119" t="n"/>
       <c r="E18" s="118" t="n"/>
       <c r="F18" s="118" t="n"/>
       <c r="G18" s="117" t="inlineStr">
@@ -10843,8 +10841,8 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="54" t="n"/>
       <c r="B19" s="54" t="n"/>
-      <c r="C19" s="55" t="n"/>
-      <c r="D19" s="55" t="n"/>
+      <c r="C19" s="119" t="n"/>
+      <c r="D19" s="119" t="n"/>
       <c r="E19" s="118" t="n"/>
       <c r="F19" s="118" t="n"/>
       <c r="G19" s="117" t="inlineStr">
@@ -10928,8 +10926,8 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="54" t="n"/>
       <c r="B21" s="54" t="n"/>
-      <c r="C21" s="55" t="n"/>
-      <c r="D21" s="55" t="n"/>
+      <c r="C21" s="119" t="n"/>
+      <c r="D21" s="119" t="n"/>
       <c r="E21" s="118" t="n"/>
       <c r="F21" s="118" t="n"/>
       <c r="G21" s="117" t="inlineStr">
@@ -11013,8 +11011,8 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="54" t="n"/>
       <c r="B23" s="54" t="n"/>
-      <c r="C23" s="55" t="n"/>
-      <c r="D23" s="55" t="n"/>
+      <c r="C23" s="119" t="n"/>
+      <c r="D23" s="119" t="n"/>
       <c r="E23" s="118" t="n"/>
       <c r="F23" s="118" t="n"/>
       <c r="G23" s="117" t="inlineStr">
@@ -11098,8 +11096,8 @@
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="54" t="n"/>
       <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="54" t="n"/>
+      <c r="C25" s="119" t="n"/>
+      <c r="D25" s="119" t="n"/>
       <c r="E25" s="118" t="n"/>
       <c r="F25" s="118" t="n"/>
       <c r="G25" s="117" t="inlineStr">
@@ -11130,8 +11128,8 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="55" t="n"/>
       <c r="B26" s="55" t="n"/>
-      <c r="C26" s="55" t="n"/>
-      <c r="D26" s="55" t="n"/>
+      <c r="C26" s="119" t="n"/>
+      <c r="D26" s="119" t="n"/>
       <c r="E26" s="118" t="n"/>
       <c r="F26" s="118" t="n"/>
       <c r="G26" s="117" t="inlineStr">
@@ -11221,8 +11219,8 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="55" t="n"/>
       <c r="B28" s="55" t="n"/>
-      <c r="C28" s="55" t="n"/>
-      <c r="D28" s="55" t="n"/>
+      <c r="C28" s="119" t="n"/>
+      <c r="D28" s="119" t="n"/>
       <c r="E28" s="118" t="n"/>
       <c r="F28" s="118" t="n"/>
       <c r="G28" s="117" t="inlineStr">
@@ -11259,23 +11257,23 @@
           <t>Move for Next Process</t>
         </is>
       </c>
-      <c r="C29" s="58" t="n"/>
-      <c r="D29" s="58" t="n"/>
-      <c r="E29" s="58" t="n"/>
-      <c r="F29" s="58" t="n"/>
-      <c r="G29" s="58" t="n"/>
-      <c r="H29" s="58" t="n"/>
-      <c r="I29" s="58" t="n"/>
-      <c r="J29" s="58" t="n"/>
-      <c r="K29" s="58" t="n"/>
-      <c r="L29" s="58" t="n"/>
-      <c r="M29" s="58" t="n"/>
-      <c r="N29" s="58" t="n"/>
-      <c r="O29" s="58" t="n"/>
-      <c r="P29" s="58" t="n"/>
-      <c r="Q29" s="58" t="n"/>
-      <c r="R29" s="58" t="n"/>
-      <c r="S29" s="59" t="n"/>
+      <c r="C29" s="119" t="n"/>
+      <c r="D29" s="119" t="n"/>
+      <c r="E29" s="119" t="n"/>
+      <c r="F29" s="119" t="n"/>
+      <c r="G29" s="119" t="n"/>
+      <c r="H29" s="119" t="n"/>
+      <c r="I29" s="119" t="n"/>
+      <c r="J29" s="119" t="n"/>
+      <c r="K29" s="119" t="n"/>
+      <c r="L29" s="119" t="n"/>
+      <c r="M29" s="119" t="n"/>
+      <c r="N29" s="119" t="n"/>
+      <c r="O29" s="119" t="n"/>
+      <c r="P29" s="119" t="n"/>
+      <c r="Q29" s="119" t="n"/>
+      <c r="R29" s="119" t="n"/>
+      <c r="S29" s="119" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="60" t="inlineStr">
@@ -11446,7 +11444,7 @@
       <c r="AL32" s="124" t="n"/>
     </row>
     <row r="33" ht="61.5" customHeight="1">
-      <c r="A33" s="131" t="n">
+      <c r="A33" s="73" t="n">
         <v>45855</v>
       </c>
       <c r="B33" s="15" t="n"/>
